--- a/target/test-classes/orange_hrm_recruitment_vacancy_testdata/vacancy.xlsx
+++ b/target/test-classes/orange_hrm_recruitment_vacancy_testdata/vacancy.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\SeleniumWorkSpaceEclipse\OrangeHRMPOM\src\test\resources\orange_hrm_recruitment_vacancy_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C853152-035D-4CF7-89ED-A734835ED792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A852CC-E138-4152-8642-8E7517C44ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="1770" windowWidth="15375" windowHeight="7785" xr2:uid="{A31B6B67-5A49-4000-919B-A5A2FCF2DDE5}"/>
+    <workbookView xWindow="9585" yWindow="2085" windowWidth="15375" windowHeight="7785" activeTab="3" xr2:uid="{A31B6B67-5A49-4000-919B-A5A2FCF2DDE5}"/>
   </bookViews>
   <sheets>
     <sheet name="VacancyData" sheetId="1" r:id="rId1"/>
+    <sheet name="HiringManager" sheetId="2" r:id="rId2"/>
+    <sheet name="AddVacancy" sheetId="3" r:id="rId3"/>
+    <sheet name="CandidatesData" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
   <si>
     <t>TestCase</t>
   </si>
@@ -64,13 +67,106 @@
   </si>
   <si>
     <t>Description-3</t>
+  </si>
+  <si>
+    <t>Test Cases</t>
+  </si>
+  <si>
+    <t>Manager Name Suggestion</t>
+  </si>
+  <si>
+    <t>TC001</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>TC005</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Vacancy Name</t>
+  </si>
+  <si>
+    <t>Number  of Positions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Java Full Stack </t>
+  </si>
+  <si>
+    <t>AI Developer</t>
+  </si>
+  <si>
+    <t>Sping boot</t>
+  </si>
+  <si>
+    <t>Git</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>firstName</t>
+  </si>
+  <si>
+    <t>lastName</t>
+  </si>
+  <si>
+    <t>middleName</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>phone number</t>
+  </si>
+  <si>
+    <t>resume url</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sanjai </t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>sanjai123@gmail.com</t>
+  </si>
+  <si>
+    <t>Sanjai</t>
+  </si>
+  <si>
+    <t>C:\\Users\\Admin\\Downloads\\AI Interviewer - Automated Candidate Evaluation using LLM.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +187,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF17C6A3"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -116,10 +226,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -127,8 +238,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -512,4 +627,194 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0557D7AC-A75E-41BC-8222-A3057E5DA793}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDF4DA-7247-411F-945C-57AD1BAB0142}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D77A11-13BF-496C-AA6C-7B5324A72184}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.140625" customWidth="1"/>
+    <col min="7" max="7" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2">
+        <v>1231231234</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="5">
+        <v>45991</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{FD02F235-6940-430E-8743-87A34D720BE8}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/target/test-classes/orange_hrm_recruitment_vacancy_testdata/vacancy.xlsx
+++ b/target/test-classes/orange_hrm_recruitment_vacancy_testdata/vacancy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\SeleniumWorkSpaceEclipse\OrangeHRMPOM\src\test\resources\orange_hrm_recruitment_vacancy_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0A852CC-E138-4152-8642-8E7517C44ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A4784E-750E-437D-9BEB-2EE7ED9A90A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9585" yWindow="2085" windowWidth="15375" windowHeight="7785" activeTab="3" xr2:uid="{A31B6B67-5A49-4000-919B-A5A2FCF2DDE5}"/>
   </bookViews>
